--- a/booking_forms/003_temporary_event_office_booking_form--booking_forms.xlsx
+++ b/booking_forms/003_temporary_event_office_booking_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -807,8 +807,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,12 +836,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'meeting'}</t>
+          <t>meeting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Meeting'}</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Conference'}</t>
+          <t>Conference</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'seminar'}</t>
+          <t>seminar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Seminar'}</t>
+          <t>Seminar</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'training'}</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Training'}</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Workshop'}</t>
+          <t>Workshop</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'8:00_am_-_9:00_am'}</t>
+          <t>8:00_am_-_9:00_am</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '8:00 AM - 9:00 AM'}</t>
+          <t>8:00 AM - 9:00 AM</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'9:00_am_-_12:00_pm'}</t>
+          <t>9:00_am_-_12:00_pm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '9:00 AM - 12:00 PM'}</t>
+          <t>9:00 AM - 12:00 PM</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'12:00_pm_-_3:00_pm'}</t>
+          <t>12:00_pm_-_3:00_pm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '12:00 PM - 3:00 PM'}</t>
+          <t>12:00 PM - 3:00 PM</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'3:00_pm_-_6:00_pm'}</t>
+          <t>3:00_pm_-_6:00_pm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '3:00 PM - 6:00 PM'}</t>
+          <t>3:00 PM - 6:00 PM</t>
         </is>
       </c>
     </row>
